--- a/entregables/MATRIZ_OBJETIVOS_ESTRATEGICOS-COTECA_OE2_corregido.xlsx
+++ b/entregables/MATRIZ_OBJETIVOS_ESTRATEGICOS-COTECA_OE2_corregido.xlsx
@@ -1339,7 +1339,7 @@
     <t>OBJETIVO ESPECIFICO 2:Implementar en un plazo de 12 meses un programa de educación y experiencia en café de especialidad, compuesto por talleres de cata, contenido educativo y experiencias cafeteras, formando una comunidad de al menos 1 800 consumidores registrados y activos y fortaleciendo la cultura cafetera en torno a la marca.</t>
   </si>
   <si>
-    <t>El objetivo declara un plazo de 6 meses, pero el cronograma, las metas y el presupuesto se despliegan en 2026 y hasta 2030, por lo que el plazo escrito no corresponde a lo programado. La meta de comunidad se repite igual en ambos horizontes (1 800 consumidores en 2026 y al 2030), de modo que no queda claro si es una meta de mantenimiento o si debía crecer año a año. Los talleres y las piezas de contenido sí crecen (de 6 a 22 talleres y de 24 a 120 piezas), lo que refuerza esa inconsistencia. Además, se mide cuántos consumidores se registran, pero no la fidelización que el objetivo promete, por lo que faltaría un indicador de participación recurrente.</t>
+    <t>Sí está alineado con la misión, puesto que la empresa se compromete a proporcionar a sus clientes una experiencia excepcional de café orgánico, y el programa de educación y experiencia acerca al consumidor al origen, a la calidad y a los métodos de preparación del café mediante talleres de cata, contenido educativo y experiencias cafeteras, transmitiendo además el trabajo sostenible que la empresa realiza junto a los caficultores. Sí está alineado con la visión, debido a que formar una comunidad de consumidores informados contribuye a que Mundo del Café sea reconocido como líder en la industria del café orgánico y como una empresa innovadora que marca la pauta en calidad, al educar al mercado y no solo venderle un producto. No está alineado con la prospección al 2050, ya que esta se enfoca en la trazabilidad total de la cadena de valor, el comercio directo con familias caficultoras, la adaptación al cambio climático y los materiales de compra de bajo impacto ambiental, mientras que el objetivo se orienta a la formación de consumidores y a la cultura cafetera; aunque el contenido educativo puede difundir el origen puneño del café, no contribuye de forma directa a los ejes de la prospección. Sí está alineado con los valores, porque responde principalmente a la Calidad, al dar a conocer y hacer degustar un café orgánico certificado y de especialidad; a la Innovación, al incorporar experiencias cafeteras y contenido educativo como nuevas formas de relacionarse con el cliente; al Respeto, al brindar al consumidor información clara sobre lo que consume; y al Trabajo en equipo, al sumar esfuerzos desde la finca hasta la taza en cada taller y experiencia. Sí está alineado con la estrategia FO de educación y experiencia, puesto que utiliza la calidad premiada del origen Esquilaya y los servicios propios de tostado y análisis de muestras (F2, F3) para formar una comunidad de consumidores, aprovechando el mayor consumo interno de café en el país (O1). Sí está alineado con las actividades A2.1, A2.2 y A2.3, ya que cada una corresponde a un componente del objetivo: realizar talleres de cata de café de especialidad, producir y difundir contenido educativo, y desarrollar experiencias cafeteras para formar la comunidad de consumidores. Sí está alineado con las subactividades, porque operativizan el cumplimiento del objetivo al detallar el proceso completo: planificar el calendario, la sede y el contenido de los talleres, convocar e inscribir participantes y registrar asistentes; definir los temas, producir las piezas educativas, publicarlas y medir su alcance; y diseñar y ejecutar las experiencias cafeteras para luego registrar y mantener activos a los participantes en la comunidad. Sí está alineado con el cronograma, debido a que establece un periodo de 12 meses durante 2026 para implementar el programa, el cual continúa ejecutándose hasta el 2030 para sostener la comunidad formada. Sí está alineado con las metas, porque fija para 2026 la realización de 6 talleres de cata, la publicación de 24 piezas de contenido educativo y la formación de una comunidad de 1 800 consumidores, y para el periodo 2026 – 2030 alcanzar 22 talleres y 120 piezas de contenido, manteniendo activa la comunidad de 1 800 consumidores. Sí está alineado con los indicadores, puesto que permiten medir el avance mediante el número de talleres de cata realizados, el número de piezas de contenido educativo publicadas y el número de consumidores registrados y activos en la comunidad. Sí está alineado con el Balanced Scorecard, puesto que el semáforo de control (verde, naranja y rojo) permite hacer seguimiento a cada meta, contribuye a la perspectiva del cliente al generar vínculo y preferencia por la marca, y fortalece la perspectiva de procesos internos al ordenar la planificación y ejecución de talleres, contenidos y experiencias. Sí está alineado con el presupuesto, debido a que requiere una inversión de S/ 14 880 en 2026 y de aproximadamente S/ 57 047 en el periodo 2026 – 2030, destinada a la sede, los insumos y el facilitador de los talleres, a la producción de contenido educativo y a la ejecución de experiencias cafeteras y el registro de la comunidad, lo que permite cumplir con el objetivo estratégico planteado.</t>
   </si>
   <si>
     <t>No esta alineado ala mision puesto que la empresa  proporciona café organico de calidad en colaboración con caficultores de manera sostenible y no consolidar presencia comercial. No esta alineado a la visión puesto que la empresa quiero convertirse líder en la industria del café organico sin la necesidad de consolidar presencia comercial. No esta alineado a la pronspección, la prospección está enfocada en la identidad, trazabilidad y sostenibilidad ambiental y no con lo comercial y táctico. si esta alineado a los valores porque responde directamente al valor de Calidad al comercializar café orgánico en puntos estratégicos, e impulsa la Innovación mediante la apertura y expansión de nuevos canales de distribución en Puno y Arequipa y refleja la Responsabilidad y el Trabajo en equipo al concretar alianzas comerciales con distribuidores, hoteles y cafeterías.Sí está alineado a la estrategia, porque la estrategia FO establece el cómo se alcanzará el objetivo comercial al utilizar la presencia local en Juliaca y los canales mayoristas actuales para posicionar el café orgánico en cafeterías, tiendas gourmet y hoteles de Puno y Juliaca, para posteriormente iniciar la expansión hacia Arequipa mediante una alianza con un distribuidor local. Si esta alineado con las actividades A1.1 y A1.2 ya que  ejecutan de forma directa y secuencial las metas operativas del objetivo especifico, cubriendo primero la colocación en los 8 puntos de venta. Si esta alineado con las subactividades operativizan el cumplimiento directo del objetivo, detallando el proceso comercial desde la captación y venta. Si esta alineado al cronograma debido a que establece un periodo de 12 meses para ejecutar las mejoras planteadas por los siguientes 3 años.Sí está alineado con las metas e indicadores, porque permite medir el avance mediante los talleres de cata, y numero de piezas de contenido educaivo publicadas y los consumidores registrados y activos de la comunidad en donde se estableceran. Sí está alineado con el Balanced Scorecard, puesto que contribuye a consolidar su presencia en Puno mediantes contenido y pruebas de cata. Sí está alineado con el presupuesto, debido a que requiere una inversión destinada a la presencia comercial en la región de Puno y su expansión a almenos 8 puntos de venta.</t>
